--- a/templates/template_kalibrasi.xlsx
+++ b/templates/template_kalibrasi.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\Proyek Coding\WORK SENSYNC\sensync-maintenance-api\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D170F85-BC0F-4710-B9C6-E828F15A29E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7A9A001-7E06-4D6F-B4D8-BCD7153DF741}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="345" yWindow="975" windowWidth="21600" windowHeight="11835" xr2:uid="{1CDA8851-BB1B-48D6-A50B-4C4097C866F2}"/>
+    <workbookView xWindow="6720" yWindow="3495" windowWidth="21600" windowHeight="11835" xr2:uid="{1CDA8851-BB1B-48D6-A50B-4C4097C866F2}"/>
   </bookViews>
   <sheets>
     <sheet name="pH" sheetId="1" r:id="rId1"/>
@@ -676,7 +676,7 @@
           </c:trendline>
           <c:xVal>
             <c:strRef>
-              <c:f>COD!$A$3:$A$5</c:f>
+              <c:f>COD!$A$3:$A$6</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -687,10 +687,10 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>COD!$B$3:$B$5</c:f>
+              <c:f>COD!$B$3:$B$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
